--- a/resources/templates/system/power_of_attorney.xlsx
+++ b/resources/templates/system/power_of_attorney.xlsx
@@ -3233,322 +3233,6 @@
     <col width="11.375" customWidth="1" style="1" min="14" max="14"/>
     <col width="26" customWidth="1" style="1" min="15" max="15"/>
     <col width="1.375" customWidth="1" style="1" min="16" max="16"/>
-    <col width="9" customWidth="1" style="1" min="17" max="257"/>
-    <col width="10" customWidth="1" style="1" min="258" max="269"/>
-    <col width="9.875" customWidth="1" style="1" min="270" max="270"/>
-    <col width="26" customWidth="1" style="1" min="271" max="271"/>
-    <col width="1.375" customWidth="1" style="1" min="272" max="272"/>
-    <col width="9" customWidth="1" style="1" min="273" max="513"/>
-    <col width="10" customWidth="1" style="1" min="514" max="525"/>
-    <col width="9.875" customWidth="1" style="1" min="526" max="526"/>
-    <col width="26" customWidth="1" style="1" min="527" max="527"/>
-    <col width="1.375" customWidth="1" style="1" min="528" max="528"/>
-    <col width="9" customWidth="1" style="1" min="529" max="769"/>
-    <col width="10" customWidth="1" style="1" min="770" max="781"/>
-    <col width="9.875" customWidth="1" style="1" min="782" max="782"/>
-    <col width="26" customWidth="1" style="1" min="783" max="783"/>
-    <col width="1.375" customWidth="1" style="1" min="784" max="784"/>
-    <col width="9" customWidth="1" style="1" min="785" max="1025"/>
-    <col width="10" customWidth="1" style="1" min="1026" max="1037"/>
-    <col width="9.875" customWidth="1" style="1" min="1038" max="1038"/>
-    <col width="26" customWidth="1" style="1" min="1039" max="1039"/>
-    <col width="1.375" customWidth="1" style="1" min="1040" max="1040"/>
-    <col width="9" customWidth="1" style="1" min="1041" max="1281"/>
-    <col width="10" customWidth="1" style="1" min="1282" max="1293"/>
-    <col width="9.875" customWidth="1" style="1" min="1294" max="1294"/>
-    <col width="26" customWidth="1" style="1" min="1295" max="1295"/>
-    <col width="1.375" customWidth="1" style="1" min="1296" max="1296"/>
-    <col width="9" customWidth="1" style="1" min="1297" max="1537"/>
-    <col width="10" customWidth="1" style="1" min="1538" max="1549"/>
-    <col width="9.875" customWidth="1" style="1" min="1550" max="1550"/>
-    <col width="26" customWidth="1" style="1" min="1551" max="1551"/>
-    <col width="1.375" customWidth="1" style="1" min="1552" max="1552"/>
-    <col width="9" customWidth="1" style="1" min="1553" max="1793"/>
-    <col width="10" customWidth="1" style="1" min="1794" max="1805"/>
-    <col width="9.875" customWidth="1" style="1" min="1806" max="1806"/>
-    <col width="26" customWidth="1" style="1" min="1807" max="1807"/>
-    <col width="1.375" customWidth="1" style="1" min="1808" max="1808"/>
-    <col width="9" customWidth="1" style="1" min="1809" max="2049"/>
-    <col width="10" customWidth="1" style="1" min="2050" max="2061"/>
-    <col width="9.875" customWidth="1" style="1" min="2062" max="2062"/>
-    <col width="26" customWidth="1" style="1" min="2063" max="2063"/>
-    <col width="1.375" customWidth="1" style="1" min="2064" max="2064"/>
-    <col width="9" customWidth="1" style="1" min="2065" max="2305"/>
-    <col width="10" customWidth="1" style="1" min="2306" max="2317"/>
-    <col width="9.875" customWidth="1" style="1" min="2318" max="2318"/>
-    <col width="26" customWidth="1" style="1" min="2319" max="2319"/>
-    <col width="1.375" customWidth="1" style="1" min="2320" max="2320"/>
-    <col width="9" customWidth="1" style="1" min="2321" max="2561"/>
-    <col width="10" customWidth="1" style="1" min="2562" max="2573"/>
-    <col width="9.875" customWidth="1" style="1" min="2574" max="2574"/>
-    <col width="26" customWidth="1" style="1" min="2575" max="2575"/>
-    <col width="1.375" customWidth="1" style="1" min="2576" max="2576"/>
-    <col width="9" customWidth="1" style="1" min="2577" max="2817"/>
-    <col width="10" customWidth="1" style="1" min="2818" max="2829"/>
-    <col width="9.875" customWidth="1" style="1" min="2830" max="2830"/>
-    <col width="26" customWidth="1" style="1" min="2831" max="2831"/>
-    <col width="1.375" customWidth="1" style="1" min="2832" max="2832"/>
-    <col width="9" customWidth="1" style="1" min="2833" max="3073"/>
-    <col width="10" customWidth="1" style="1" min="3074" max="3085"/>
-    <col width="9.875" customWidth="1" style="1" min="3086" max="3086"/>
-    <col width="26" customWidth="1" style="1" min="3087" max="3087"/>
-    <col width="1.375" customWidth="1" style="1" min="3088" max="3088"/>
-    <col width="9" customWidth="1" style="1" min="3089" max="3329"/>
-    <col width="10" customWidth="1" style="1" min="3330" max="3341"/>
-    <col width="9.875" customWidth="1" style="1" min="3342" max="3342"/>
-    <col width="26" customWidth="1" style="1" min="3343" max="3343"/>
-    <col width="1.375" customWidth="1" style="1" min="3344" max="3344"/>
-    <col width="9" customWidth="1" style="1" min="3345" max="3585"/>
-    <col width="10" customWidth="1" style="1" min="3586" max="3597"/>
-    <col width="9.875" customWidth="1" style="1" min="3598" max="3598"/>
-    <col width="26" customWidth="1" style="1" min="3599" max="3599"/>
-    <col width="1.375" customWidth="1" style="1" min="3600" max="3600"/>
-    <col width="9" customWidth="1" style="1" min="3601" max="3841"/>
-    <col width="10" customWidth="1" style="1" min="3842" max="3853"/>
-    <col width="9.875" customWidth="1" style="1" min="3854" max="3854"/>
-    <col width="26" customWidth="1" style="1" min="3855" max="3855"/>
-    <col width="1.375" customWidth="1" style="1" min="3856" max="3856"/>
-    <col width="9" customWidth="1" style="1" min="3857" max="4097"/>
-    <col width="10" customWidth="1" style="1" min="4098" max="4109"/>
-    <col width="9.875" customWidth="1" style="1" min="4110" max="4110"/>
-    <col width="26" customWidth="1" style="1" min="4111" max="4111"/>
-    <col width="1.375" customWidth="1" style="1" min="4112" max="4112"/>
-    <col width="9" customWidth="1" style="1" min="4113" max="4353"/>
-    <col width="10" customWidth="1" style="1" min="4354" max="4365"/>
-    <col width="9.875" customWidth="1" style="1" min="4366" max="4366"/>
-    <col width="26" customWidth="1" style="1" min="4367" max="4367"/>
-    <col width="1.375" customWidth="1" style="1" min="4368" max="4368"/>
-    <col width="9" customWidth="1" style="1" min="4369" max="4609"/>
-    <col width="10" customWidth="1" style="1" min="4610" max="4621"/>
-    <col width="9.875" customWidth="1" style="1" min="4622" max="4622"/>
-    <col width="26" customWidth="1" style="1" min="4623" max="4623"/>
-    <col width="1.375" customWidth="1" style="1" min="4624" max="4624"/>
-    <col width="9" customWidth="1" style="1" min="4625" max="4865"/>
-    <col width="10" customWidth="1" style="1" min="4866" max="4877"/>
-    <col width="9.875" customWidth="1" style="1" min="4878" max="4878"/>
-    <col width="26" customWidth="1" style="1" min="4879" max="4879"/>
-    <col width="1.375" customWidth="1" style="1" min="4880" max="4880"/>
-    <col width="9" customWidth="1" style="1" min="4881" max="5121"/>
-    <col width="10" customWidth="1" style="1" min="5122" max="5133"/>
-    <col width="9.875" customWidth="1" style="1" min="5134" max="5134"/>
-    <col width="26" customWidth="1" style="1" min="5135" max="5135"/>
-    <col width="1.375" customWidth="1" style="1" min="5136" max="5136"/>
-    <col width="9" customWidth="1" style="1" min="5137" max="5377"/>
-    <col width="10" customWidth="1" style="1" min="5378" max="5389"/>
-    <col width="9.875" customWidth="1" style="1" min="5390" max="5390"/>
-    <col width="26" customWidth="1" style="1" min="5391" max="5391"/>
-    <col width="1.375" customWidth="1" style="1" min="5392" max="5392"/>
-    <col width="9" customWidth="1" style="1" min="5393" max="5633"/>
-    <col width="10" customWidth="1" style="1" min="5634" max="5645"/>
-    <col width="9.875" customWidth="1" style="1" min="5646" max="5646"/>
-    <col width="26" customWidth="1" style="1" min="5647" max="5647"/>
-    <col width="1.375" customWidth="1" style="1" min="5648" max="5648"/>
-    <col width="9" customWidth="1" style="1" min="5649" max="5889"/>
-    <col width="10" customWidth="1" style="1" min="5890" max="5901"/>
-    <col width="9.875" customWidth="1" style="1" min="5902" max="5902"/>
-    <col width="26" customWidth="1" style="1" min="5903" max="5903"/>
-    <col width="1.375" customWidth="1" style="1" min="5904" max="5904"/>
-    <col width="9" customWidth="1" style="1" min="5905" max="6145"/>
-    <col width="10" customWidth="1" style="1" min="6146" max="6157"/>
-    <col width="9.875" customWidth="1" style="1" min="6158" max="6158"/>
-    <col width="26" customWidth="1" style="1" min="6159" max="6159"/>
-    <col width="1.375" customWidth="1" style="1" min="6160" max="6160"/>
-    <col width="9" customWidth="1" style="1" min="6161" max="6401"/>
-    <col width="10" customWidth="1" style="1" min="6402" max="6413"/>
-    <col width="9.875" customWidth="1" style="1" min="6414" max="6414"/>
-    <col width="26" customWidth="1" style="1" min="6415" max="6415"/>
-    <col width="1.375" customWidth="1" style="1" min="6416" max="6416"/>
-    <col width="9" customWidth="1" style="1" min="6417" max="6657"/>
-    <col width="10" customWidth="1" style="1" min="6658" max="6669"/>
-    <col width="9.875" customWidth="1" style="1" min="6670" max="6670"/>
-    <col width="26" customWidth="1" style="1" min="6671" max="6671"/>
-    <col width="1.375" customWidth="1" style="1" min="6672" max="6672"/>
-    <col width="9" customWidth="1" style="1" min="6673" max="6913"/>
-    <col width="10" customWidth="1" style="1" min="6914" max="6925"/>
-    <col width="9.875" customWidth="1" style="1" min="6926" max="6926"/>
-    <col width="26" customWidth="1" style="1" min="6927" max="6927"/>
-    <col width="1.375" customWidth="1" style="1" min="6928" max="6928"/>
-    <col width="9" customWidth="1" style="1" min="6929" max="7169"/>
-    <col width="10" customWidth="1" style="1" min="7170" max="7181"/>
-    <col width="9.875" customWidth="1" style="1" min="7182" max="7182"/>
-    <col width="26" customWidth="1" style="1" min="7183" max="7183"/>
-    <col width="1.375" customWidth="1" style="1" min="7184" max="7184"/>
-    <col width="9" customWidth="1" style="1" min="7185" max="7425"/>
-    <col width="10" customWidth="1" style="1" min="7426" max="7437"/>
-    <col width="9.875" customWidth="1" style="1" min="7438" max="7438"/>
-    <col width="26" customWidth="1" style="1" min="7439" max="7439"/>
-    <col width="1.375" customWidth="1" style="1" min="7440" max="7440"/>
-    <col width="9" customWidth="1" style="1" min="7441" max="7681"/>
-    <col width="10" customWidth="1" style="1" min="7682" max="7693"/>
-    <col width="9.875" customWidth="1" style="1" min="7694" max="7694"/>
-    <col width="26" customWidth="1" style="1" min="7695" max="7695"/>
-    <col width="1.375" customWidth="1" style="1" min="7696" max="7696"/>
-    <col width="9" customWidth="1" style="1" min="7697" max="7937"/>
-    <col width="10" customWidth="1" style="1" min="7938" max="7949"/>
-    <col width="9.875" customWidth="1" style="1" min="7950" max="7950"/>
-    <col width="26" customWidth="1" style="1" min="7951" max="7951"/>
-    <col width="1.375" customWidth="1" style="1" min="7952" max="7952"/>
-    <col width="9" customWidth="1" style="1" min="7953" max="8193"/>
-    <col width="10" customWidth="1" style="1" min="8194" max="8205"/>
-    <col width="9.875" customWidth="1" style="1" min="8206" max="8206"/>
-    <col width="26" customWidth="1" style="1" min="8207" max="8207"/>
-    <col width="1.375" customWidth="1" style="1" min="8208" max="8208"/>
-    <col width="9" customWidth="1" style="1" min="8209" max="8449"/>
-    <col width="10" customWidth="1" style="1" min="8450" max="8461"/>
-    <col width="9.875" customWidth="1" style="1" min="8462" max="8462"/>
-    <col width="26" customWidth="1" style="1" min="8463" max="8463"/>
-    <col width="1.375" customWidth="1" style="1" min="8464" max="8464"/>
-    <col width="9" customWidth="1" style="1" min="8465" max="8705"/>
-    <col width="10" customWidth="1" style="1" min="8706" max="8717"/>
-    <col width="9.875" customWidth="1" style="1" min="8718" max="8718"/>
-    <col width="26" customWidth="1" style="1" min="8719" max="8719"/>
-    <col width="1.375" customWidth="1" style="1" min="8720" max="8720"/>
-    <col width="9" customWidth="1" style="1" min="8721" max="8961"/>
-    <col width="10" customWidth="1" style="1" min="8962" max="8973"/>
-    <col width="9.875" customWidth="1" style="1" min="8974" max="8974"/>
-    <col width="26" customWidth="1" style="1" min="8975" max="8975"/>
-    <col width="1.375" customWidth="1" style="1" min="8976" max="8976"/>
-    <col width="9" customWidth="1" style="1" min="8977" max="9217"/>
-    <col width="10" customWidth="1" style="1" min="9218" max="9229"/>
-    <col width="9.875" customWidth="1" style="1" min="9230" max="9230"/>
-    <col width="26" customWidth="1" style="1" min="9231" max="9231"/>
-    <col width="1.375" customWidth="1" style="1" min="9232" max="9232"/>
-    <col width="9" customWidth="1" style="1" min="9233" max="9473"/>
-    <col width="10" customWidth="1" style="1" min="9474" max="9485"/>
-    <col width="9.875" customWidth="1" style="1" min="9486" max="9486"/>
-    <col width="26" customWidth="1" style="1" min="9487" max="9487"/>
-    <col width="1.375" customWidth="1" style="1" min="9488" max="9488"/>
-    <col width="9" customWidth="1" style="1" min="9489" max="9729"/>
-    <col width="10" customWidth="1" style="1" min="9730" max="9741"/>
-    <col width="9.875" customWidth="1" style="1" min="9742" max="9742"/>
-    <col width="26" customWidth="1" style="1" min="9743" max="9743"/>
-    <col width="1.375" customWidth="1" style="1" min="9744" max="9744"/>
-    <col width="9" customWidth="1" style="1" min="9745" max="9985"/>
-    <col width="10" customWidth="1" style="1" min="9986" max="9997"/>
-    <col width="9.875" customWidth="1" style="1" min="9998" max="9998"/>
-    <col width="26" customWidth="1" style="1" min="9999" max="9999"/>
-    <col width="1.375" customWidth="1" style="1" min="10000" max="10000"/>
-    <col width="9" customWidth="1" style="1" min="10001" max="10241"/>
-    <col width="10" customWidth="1" style="1" min="10242" max="10253"/>
-    <col width="9.875" customWidth="1" style="1" min="10254" max="10254"/>
-    <col width="26" customWidth="1" style="1" min="10255" max="10255"/>
-    <col width="1.375" customWidth="1" style="1" min="10256" max="10256"/>
-    <col width="9" customWidth="1" style="1" min="10257" max="10497"/>
-    <col width="10" customWidth="1" style="1" min="10498" max="10509"/>
-    <col width="9.875" customWidth="1" style="1" min="10510" max="10510"/>
-    <col width="26" customWidth="1" style="1" min="10511" max="10511"/>
-    <col width="1.375" customWidth="1" style="1" min="10512" max="10512"/>
-    <col width="9" customWidth="1" style="1" min="10513" max="10753"/>
-    <col width="10" customWidth="1" style="1" min="10754" max="10765"/>
-    <col width="9.875" customWidth="1" style="1" min="10766" max="10766"/>
-    <col width="26" customWidth="1" style="1" min="10767" max="10767"/>
-    <col width="1.375" customWidth="1" style="1" min="10768" max="10768"/>
-    <col width="9" customWidth="1" style="1" min="10769" max="11009"/>
-    <col width="10" customWidth="1" style="1" min="11010" max="11021"/>
-    <col width="9.875" customWidth="1" style="1" min="11022" max="11022"/>
-    <col width="26" customWidth="1" style="1" min="11023" max="11023"/>
-    <col width="1.375" customWidth="1" style="1" min="11024" max="11024"/>
-    <col width="9" customWidth="1" style="1" min="11025" max="11265"/>
-    <col width="10" customWidth="1" style="1" min="11266" max="11277"/>
-    <col width="9.875" customWidth="1" style="1" min="11278" max="11278"/>
-    <col width="26" customWidth="1" style="1" min="11279" max="11279"/>
-    <col width="1.375" customWidth="1" style="1" min="11280" max="11280"/>
-    <col width="9" customWidth="1" style="1" min="11281" max="11521"/>
-    <col width="10" customWidth="1" style="1" min="11522" max="11533"/>
-    <col width="9.875" customWidth="1" style="1" min="11534" max="11534"/>
-    <col width="26" customWidth="1" style="1" min="11535" max="11535"/>
-    <col width="1.375" customWidth="1" style="1" min="11536" max="11536"/>
-    <col width="9" customWidth="1" style="1" min="11537" max="11777"/>
-    <col width="10" customWidth="1" style="1" min="11778" max="11789"/>
-    <col width="9.875" customWidth="1" style="1" min="11790" max="11790"/>
-    <col width="26" customWidth="1" style="1" min="11791" max="11791"/>
-    <col width="1.375" customWidth="1" style="1" min="11792" max="11792"/>
-    <col width="9" customWidth="1" style="1" min="11793" max="12033"/>
-    <col width="10" customWidth="1" style="1" min="12034" max="12045"/>
-    <col width="9.875" customWidth="1" style="1" min="12046" max="12046"/>
-    <col width="26" customWidth="1" style="1" min="12047" max="12047"/>
-    <col width="1.375" customWidth="1" style="1" min="12048" max="12048"/>
-    <col width="9" customWidth="1" style="1" min="12049" max="12289"/>
-    <col width="10" customWidth="1" style="1" min="12290" max="12301"/>
-    <col width="9.875" customWidth="1" style="1" min="12302" max="12302"/>
-    <col width="26" customWidth="1" style="1" min="12303" max="12303"/>
-    <col width="1.375" customWidth="1" style="1" min="12304" max="12304"/>
-    <col width="9" customWidth="1" style="1" min="12305" max="12545"/>
-    <col width="10" customWidth="1" style="1" min="12546" max="12557"/>
-    <col width="9.875" customWidth="1" style="1" min="12558" max="12558"/>
-    <col width="26" customWidth="1" style="1" min="12559" max="12559"/>
-    <col width="1.375" customWidth="1" style="1" min="12560" max="12560"/>
-    <col width="9" customWidth="1" style="1" min="12561" max="12801"/>
-    <col width="10" customWidth="1" style="1" min="12802" max="12813"/>
-    <col width="9.875" customWidth="1" style="1" min="12814" max="12814"/>
-    <col width="26" customWidth="1" style="1" min="12815" max="12815"/>
-    <col width="1.375" customWidth="1" style="1" min="12816" max="12816"/>
-    <col width="9" customWidth="1" style="1" min="12817" max="13057"/>
-    <col width="10" customWidth="1" style="1" min="13058" max="13069"/>
-    <col width="9.875" customWidth="1" style="1" min="13070" max="13070"/>
-    <col width="26" customWidth="1" style="1" min="13071" max="13071"/>
-    <col width="1.375" customWidth="1" style="1" min="13072" max="13072"/>
-    <col width="9" customWidth="1" style="1" min="13073" max="13313"/>
-    <col width="10" customWidth="1" style="1" min="13314" max="13325"/>
-    <col width="9.875" customWidth="1" style="1" min="13326" max="13326"/>
-    <col width="26" customWidth="1" style="1" min="13327" max="13327"/>
-    <col width="1.375" customWidth="1" style="1" min="13328" max="13328"/>
-    <col width="9" customWidth="1" style="1" min="13329" max="13569"/>
-    <col width="10" customWidth="1" style="1" min="13570" max="13581"/>
-    <col width="9.875" customWidth="1" style="1" min="13582" max="13582"/>
-    <col width="26" customWidth="1" style="1" min="13583" max="13583"/>
-    <col width="1.375" customWidth="1" style="1" min="13584" max="13584"/>
-    <col width="9" customWidth="1" style="1" min="13585" max="13825"/>
-    <col width="10" customWidth="1" style="1" min="13826" max="13837"/>
-    <col width="9.875" customWidth="1" style="1" min="13838" max="13838"/>
-    <col width="26" customWidth="1" style="1" min="13839" max="13839"/>
-    <col width="1.375" customWidth="1" style="1" min="13840" max="13840"/>
-    <col width="9" customWidth="1" style="1" min="13841" max="14081"/>
-    <col width="10" customWidth="1" style="1" min="14082" max="14093"/>
-    <col width="9.875" customWidth="1" style="1" min="14094" max="14094"/>
-    <col width="26" customWidth="1" style="1" min="14095" max="14095"/>
-    <col width="1.375" customWidth="1" style="1" min="14096" max="14096"/>
-    <col width="9" customWidth="1" style="1" min="14097" max="14337"/>
-    <col width="10" customWidth="1" style="1" min="14338" max="14349"/>
-    <col width="9.875" customWidth="1" style="1" min="14350" max="14350"/>
-    <col width="26" customWidth="1" style="1" min="14351" max="14351"/>
-    <col width="1.375" customWidth="1" style="1" min="14352" max="14352"/>
-    <col width="9" customWidth="1" style="1" min="14353" max="14593"/>
-    <col width="10" customWidth="1" style="1" min="14594" max="14605"/>
-    <col width="9.875" customWidth="1" style="1" min="14606" max="14606"/>
-    <col width="26" customWidth="1" style="1" min="14607" max="14607"/>
-    <col width="1.375" customWidth="1" style="1" min="14608" max="14608"/>
-    <col width="9" customWidth="1" style="1" min="14609" max="14849"/>
-    <col width="10" customWidth="1" style="1" min="14850" max="14861"/>
-    <col width="9.875" customWidth="1" style="1" min="14862" max="14862"/>
-    <col width="26" customWidth="1" style="1" min="14863" max="14863"/>
-    <col width="1.375" customWidth="1" style="1" min="14864" max="14864"/>
-    <col width="9" customWidth="1" style="1" min="14865" max="15105"/>
-    <col width="10" customWidth="1" style="1" min="15106" max="15117"/>
-    <col width="9.875" customWidth="1" style="1" min="15118" max="15118"/>
-    <col width="26" customWidth="1" style="1" min="15119" max="15119"/>
-    <col width="1.375" customWidth="1" style="1" min="15120" max="15120"/>
-    <col width="9" customWidth="1" style="1" min="15121" max="15361"/>
-    <col width="10" customWidth="1" style="1" min="15362" max="15373"/>
-    <col width="9.875" customWidth="1" style="1" min="15374" max="15374"/>
-    <col width="26" customWidth="1" style="1" min="15375" max="15375"/>
-    <col width="1.375" customWidth="1" style="1" min="15376" max="15376"/>
-    <col width="9" customWidth="1" style="1" min="15377" max="15617"/>
-    <col width="10" customWidth="1" style="1" min="15618" max="15629"/>
-    <col width="9.875" customWidth="1" style="1" min="15630" max="15630"/>
-    <col width="26" customWidth="1" style="1" min="15631" max="15631"/>
-    <col width="1.375" customWidth="1" style="1" min="15632" max="15632"/>
-    <col width="9" customWidth="1" style="1" min="15633" max="15873"/>
-    <col width="10" customWidth="1" style="1" min="15874" max="15885"/>
-    <col width="9.875" customWidth="1" style="1" min="15886" max="15886"/>
-    <col width="26" customWidth="1" style="1" min="15887" max="15887"/>
-    <col width="1.375" customWidth="1" style="1" min="15888" max="15888"/>
-    <col width="9" customWidth="1" style="1" min="15889" max="16129"/>
-    <col width="10" customWidth="1" style="1" min="16130" max="16141"/>
-    <col width="9.875" customWidth="1" style="1" min="16142" max="16142"/>
-    <col width="26" customWidth="1" style="1" min="16143" max="16143"/>
-    <col width="1.375" customWidth="1" style="1" min="16144" max="16144"/>
-    <col width="9" customWidth="1" style="1" min="16145" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="55.5" customHeight="1" s="26">
